--- a/Indomie Clients Details/Aslam Super Mart.xlsx
+++ b/Indomie Clients Details/Aslam Super Mart.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E55BA40-34B9-46C9-9436-793F69938E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB46968-8935-423F-B995-32131ECCEB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3383,7 +3383,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3411,7 +3411,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4628,7 +4628,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4656,7 +4656,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5873,7 +5873,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5901,7 +5901,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7118,7 +7118,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7146,7 +7146,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8363,7 +8363,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8391,7 +8391,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9608,7 +9608,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9636,7 +9636,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10853,7 +10853,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10881,7 +10881,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12098,7 +12098,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12126,7 +12126,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13343,7 +13343,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13371,7 +13371,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14588,7 +14588,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14616,7 +14616,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18583,7 +18583,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18611,7 +18611,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19825,7 +19825,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19853,7 +19853,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21066,7 +21066,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21094,7 +21094,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22307,7 +22307,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22335,7 +22335,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23553,7 +23553,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23581,7 +23581,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>78333.580907999989</v>
+        <v>59554.578567660006</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23878,11 +23878,11 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>400</v>
+        <v>314</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>20985</v>
+        <v>16473.224999999999</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23894,23 +23894,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>2518.1999999999998</v>
+        <v>1976.7869999999998</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>18466.8</v>
+        <v>14496.437999999998</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>3324.0239999999999</v>
+        <v>2609.3588399999999</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>108.95412</v>
+        <v>85.528984199999996</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>21899.778119999999</v>
+        <v>17191.325824199997</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23952,11 +23952,11 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>20985</v>
+        <v>18519.262500000001</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
@@ -23968,23 +23968,23 @@
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>2518.1999999999998</v>
+        <v>2222.3114999999998</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>18466.8</v>
+        <v>16296.951000000001</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>3324.0239999999999</v>
+        <v>2933.45118</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>108.95412</v>
+        <v>96.152010899999993</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>21899.778119999999</v>
+        <v>19326.554190900002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24026,11 +24026,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18</f>
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>20985</v>
+        <v>20355.45</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
@@ -24042,23 +24042,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>2518.1999999999998</v>
+        <v>2442.6539999999995</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>18466.8</v>
+        <v>17912.796000000002</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>3324.0239999999999</v>
+        <v>3224.3032799999996</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>108.95412</v>
+        <v>105.68549639999999</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>21899.778119999999</v>
+        <v>21242.784776400003</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24096,11 +24096,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>29056</v>
+        <v>25424</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24112,23 +24112,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>3486.72</v>
+        <v>3050.88</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>25569.279999999999</v>
+        <v>22373.119999999999</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>4602.4703999999992</v>
+        <v>4027.1615999999995</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>150.85875199999998</v>
+        <v>132.001408</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>30322.609151999997</v>
+        <v>26532.283007999999</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24166,11 +24166,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>400</v>
+        <v>311</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>29056</v>
+        <v>22591.040000000001</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -24182,23 +24182,23 @@
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>3486.72</v>
+        <v>2710.9247999999998</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>25569.279999999999</v>
+        <v>19880.1152</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>4602.4703999999992</v>
+        <v>3578.4207359999996</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>150.85875199999998</v>
+        <v>117.29267967999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>30322.609151999997</v>
+        <v>23575.828615679999</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24236,11 +24236,11 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>29056</v>
+        <v>28765.439999999999</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -24252,23 +24252,23 @@
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>3486.72</v>
+        <v>3451.8527999999997</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>25569.279999999999</v>
+        <v>25313.587199999998</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>4602.4703999999992</v>
+        <v>4556.4456959999998</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>150.85875199999998</v>
+        <v>149.35016447999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>30322.609151999997</v>
+        <v>30019.383060479999</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24496,7 +24496,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>60</v>
+        <v>52.8</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24507,11 +24507,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>2400</v>
+        <v>2112</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>150123</v>
+        <v>132128.41750000001</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24523,23 +24523,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>18014.759999999998</v>
+        <v>15855.410100000001</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>132108.24</v>
+        <v>116273.00739999999</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>23779.483199999995</v>
+        <v>20929.141331999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>779.43861600000002</v>
+        <v>686.01074366</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>156667.16181599998</v>
+        <v>137888.15947566001</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24747,7 +24747,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>156667.16181599998</v>
+        <v>137888.15947566001</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24780,7 +24780,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>150123</v>
+        <v>132128.41750000001</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24801,7 +24801,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>18014.759999999998</v>
+        <v>15855.410100000001</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24844,7 +24844,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>132108.24</v>
+        <v>116273.0074</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>23779.483199999995</v>
+        <v>20929.141331999999</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24891,7 +24891,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>155887.72319999998</v>
+        <v>137202.148732</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>3897.1930799999996</v>
+        <v>3430.0537183000001</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24926,7 +24926,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>159784.91627999998</v>
+        <v>140632.20245030001</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25098,7 +25098,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25126,7 +25126,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25419,11 +25419,11 @@
       </c>
       <c r="G16" s="99"/>
       <c r="H16" s="100">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>10492.5</v>
+        <v>5980.7249999999995</v>
       </c>
       <c r="J16" s="102">
         <v>0</v>
@@ -25434,23 +25434,23 @@
       </c>
       <c r="L16" s="104">
         <f>I16*12%</f>
-        <v>1259.0999999999999</v>
+        <v>717.6869999999999</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>9233.4</v>
+        <v>5263.0379999999996</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>1662.0119999999999</v>
+        <v>947.34683999999993</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>54.477060000000002</v>
+        <v>31.051924199999998</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>10949.88906</v>
+        <v>6241.4367641999997</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25483,11 +25483,11 @@
       </c>
       <c r="G17" s="113"/>
       <c r="H17" s="114">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
-        <v>10492.5</v>
+        <v>8026.7624999999998</v>
       </c>
       <c r="J17" s="116">
         <v>0</v>
@@ -25498,23 +25498,23 @@
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="5">I17*12%</f>
-        <v>1259.0999999999999</v>
+        <v>963.21149999999989</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
-        <v>9233.4</v>
+        <v>7063.5509999999995</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>1662.0119999999999</v>
+        <v>1271.4391799999999</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>54.477060000000002</v>
+        <v>41.674950899999992</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>10949.88906</v>
+        <v>8376.665130899999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25547,11 +25547,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>10492.5</v>
+        <v>9862.9499999999989</v>
       </c>
       <c r="J18" s="116">
         <v>0</v>
@@ -25562,23 +25562,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>1259.0999999999999</v>
+        <v>1183.5539999999999</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>9233.4</v>
+        <v>8679.3959999999988</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>1662.0119999999999</v>
+        <v>1562.2912799999997</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>54.477060000000002</v>
+        <v>51.208436399999989</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>10949.88906</v>
+        <v>10292.895716399998</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25607,11 +25607,11 @@
       </c>
       <c r="G19" s="113"/>
       <c r="H19" s="114">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="3"/>
-        <v>14528</v>
+        <v>10896</v>
       </c>
       <c r="J19" s="116">
         <v>0</v>
@@ -25622,23 +25622,23 @@
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>1743.36</v>
+        <v>1307.52</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>12784.64</v>
+        <v>9588.48</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>2301.2351999999996</v>
+        <v>1725.9263999999998</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>75.429375999999991</v>
+        <v>56.572032</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>15161.304575999999</v>
+        <v>11370.978432</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25667,11 +25667,11 @@
       </c>
       <c r="G20" s="113"/>
       <c r="H20" s="114">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>14528</v>
+        <v>8063.04</v>
       </c>
       <c r="J20" s="116">
         <v>0</v>
@@ -25682,23 +25682,23 @@
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>1743.36</v>
+        <v>967.56479999999999</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>12784.64</v>
+        <v>7095.4751999999999</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>2301.2351999999996</v>
+        <v>1277.185536</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>75.429375999999991</v>
+        <v>41.863303680000001</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>15161.304575999999</v>
+        <v>8414.52403968</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25727,11 +25727,11 @@
       </c>
       <c r="G21" s="113"/>
       <c r="H21" s="114">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I21" s="115">
         <f t="shared" si="3"/>
-        <v>14528</v>
+        <v>14237.44</v>
       </c>
       <c r="J21" s="116">
         <v>0</v>
@@ -25742,23 +25742,23 @@
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
-        <v>1743.36</v>
+        <v>1708.4928</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>12784.64</v>
+        <v>12528.947200000001</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>2301.2351999999996</v>
+        <v>2255.2104960000001</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>75.429375999999991</v>
+        <v>73.920788479999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>15161.304575999999</v>
+        <v>14858.07848448</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25946,11 +25946,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>1200</v>
+        <v>912</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>75061.5</v>
+        <v>57066.917500000003</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
@@ -25962,23 +25962,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>9007.3799999999992</v>
+        <v>6848.0300999999999</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>66054.12</v>
+        <v>50218.8874</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>11889.741599999998</v>
+        <v>9039.3997319999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>389.71930800000001</v>
+        <v>296.29143565999999</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>78333.580907999989</v>
+        <v>59554.578567659992</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26028,7 +26028,7 @@
       <c r="O28" s="223"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>75061.5</v>
+        <v>57066.917500000003</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26049,7 +26049,7 @@
       <c r="O29" s="225"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>9007.3799999999992</v>
+        <v>6848.0300999999999</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26092,7 +26092,7 @@
       <c r="O31" s="225"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>66054.12</v>
+        <v>50218.887400000007</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>11889.741599999998</v>
+        <v>9039.3997319999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26139,7 +26139,7 @@
       <c r="O33" s="227"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>77943.861599999989</v>
+        <v>59258.287132000005</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>389.71930799999996</v>
+        <v>296.29143566000005</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26174,7 +26174,7 @@
       <c r="O35" s="205"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>78333.580907999989</v>
+        <v>59554.578567660006</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26346,7 +26346,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26374,7 +26374,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27591,7 +27591,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27619,7 +27619,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28835,7 +28835,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28863,7 +28863,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30080,7 +30080,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30108,7 +30108,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31326,7 +31326,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31354,7 +31354,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
